--- a/Clean_data/Master_Dataset.xlsx
+++ b/Clean_data/Master_Dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOWNLOADS new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Desktop\Research_Project_colab_TSA_DATA\Clean_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707D4CCC-7A61-42EC-85D6-673D65F2408B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1B9102-3DFD-44E5-9134-9286D955B255}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16596" windowHeight="5556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
